--- a/artfynd/A 15831-2026 artfynd.xlsx
+++ b/artfynd/A 15831-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94523116</v>
+        <v>94523134</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463869.1017777031</v>
+        <v>463867</v>
       </c>
       <c r="R2" t="n">
-        <v>7104916.27417447</v>
+        <v>7104904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,54 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94490509</v>
+        <v>94523145</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464057.2253953741</v>
+        <v>463831</v>
       </c>
       <c r="R3" t="n">
-        <v>7104657.547404063</v>
+        <v>7104886</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,54 +840,40 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94580775</v>
+        <v>94523116</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,17 +901,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464050.7903082664</v>
+        <v>463869</v>
       </c>
       <c r="R4" t="n">
-        <v>7104631.790958654</v>
+        <v>7104916</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,19 +938,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,60 +960,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91847547</v>
+        <v>94523143</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Torshöjden - Sörrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464704.8987313994</v>
+        <v>464003</v>
       </c>
       <c r="R5" t="n">
-        <v>7104752.1338409</v>
+        <v>7104699</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,22 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,31 +1052,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94580779</v>
+        <v>94580775</v>
       </c>
       <c r="B6" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464563.1710386831</v>
+        <v>464051</v>
       </c>
       <c r="R6" t="n">
-        <v>7104663.121644213</v>
+        <v>7104632</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,19 +1132,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91847584</v>
+        <v>91847572</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464447.8257088873</v>
+        <v>464719</v>
       </c>
       <c r="R7" t="n">
-        <v>7104160.044302321</v>
+        <v>7104715</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1313,19 +1229,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91847585</v>
+        <v>91847547</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464447.8257088873</v>
+        <v>464705</v>
       </c>
       <c r="R8" t="n">
-        <v>7104160.044302321</v>
+        <v>7104752</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,19 +1330,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,15 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91847627</v>
+        <v>91847571</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464389.8314009494</v>
+        <v>464719</v>
       </c>
       <c r="R9" t="n">
-        <v>7104187.856287077</v>
+        <v>7104715</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1545,19 +1431,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,37 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91847628</v>
+        <v>91847574</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464434.0578151146</v>
+        <v>464719</v>
       </c>
       <c r="R10" t="n">
-        <v>7104182.971323023</v>
+        <v>7104715</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,19 +1532,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,37 +1565,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91953585</v>
+        <v>91847573</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1744,13 +1600,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463757.9931134701</v>
+        <v>464719</v>
       </c>
       <c r="R11" t="n">
-        <v>7104259.086236862</v>
+        <v>7104715</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,24 +1633,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,15 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94489922</v>
+        <v>94580779</v>
       </c>
       <c r="B12" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,39 +1677,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Myhrbodarna, Valsjöbyn, Jmt, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464227.6499595161</v>
+        <v>464563</v>
       </c>
       <c r="R12" t="n">
-        <v>7104381.938951407</v>
+        <v>7104663</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,19 +1734,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,27 +1751,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lisa Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94489320</v>
+        <v>91847585</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,35 +1774,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463973.8958438191</v>
+        <v>464448</v>
       </c>
       <c r="R13" t="n">
-        <v>7104540.7390351</v>
+        <v>7104160</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,22 +1828,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,58 +1853,56 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94489368</v>
+        <v>91847627</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464027.7552437605</v>
+        <v>464390</v>
       </c>
       <c r="R14" t="n">
-        <v>7104459.554336783</v>
+        <v>7104188</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,22 +1929,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,61 +1954,59 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94489686</v>
+        <v>91953585</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krokom, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464602.0134415099</v>
+        <v>463758</v>
       </c>
       <c r="R15" t="n">
-        <v>7104262.936026884</v>
+        <v>7104259</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,22 +2030,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,26 +2060,25 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94523140</v>
+        <v>94489320</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2312,19 +2100,20 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463815.4605240455</v>
+        <v>463973</v>
       </c>
       <c r="R16" t="n">
-        <v>7104261.91981072</v>
+        <v>7104541</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2351,19 +2140,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,15 +2157,605 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94489368</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Krokom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>464028</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7104460</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>94523140</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torshöjden - Sörrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>463815</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7104262</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>91847584</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>464448</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7104160</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>94489530</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Krokom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>464271</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7104281</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94489922</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Krokom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>464228</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7104382</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94489481</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Krokom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>464221</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7104290</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15831-2026 artfynd.xlsx
+++ b/artfynd/A 15831-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523134</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523143</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94580775</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847572</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847547</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847574</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847573</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94580779</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847585</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847627</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953585</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2166,6 +2241,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94489320</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94489368</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523140</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847584</t>
         </is>
       </c>
     </row>
@@ -2562,6 +2657,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94489530</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94489922</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2756,8 +2861,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94489481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>